--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_lubrication_system_clustering/clustering/dsas_g11_lubrication/clustering_g11_lubrication_output2.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_lubrication_system_clustering/clustering/dsas_g11_lubrication/clustering_g11_lubrication_output2.xlsx
@@ -608,11 +608,11 @@
         <v>24</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8187025255968281</v>
+        <v>0.8501065966409839</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
         <v>24</v>
       </c>
       <c r="U3" t="n">
-        <v>0.99453795342452</v>
+        <v>1.01856540379691</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>24</v>
       </c>
       <c r="U4" t="n">
-        <v>1.188473565446051</v>
+        <v>1.206980321940013</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.189271927884327</v>
+        <v>1.209333522495658</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>24</v>
       </c>
       <c r="U6" t="n">
-        <v>1.189271927884327</v>
+        <v>1.209333522495658</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
         <v>24</v>
       </c>
       <c r="U7" t="n">
-        <v>1.189271927884327</v>
+        <v>1.209333522495658</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.189271927884327</v>
+        <v>1.209333522495658</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>24</v>
       </c>
       <c r="U9" t="n">
-        <v>1.189271927884327</v>
+        <v>1.209333522495658</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>24</v>
       </c>
       <c r="U10" t="n">
-        <v>1.169381246642363</v>
+        <v>1.18978822110398</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.149641909406004</v>
+        <v>1.170403848080069</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.135616046880445</v>
+        <v>1.158276255028514</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>24</v>
       </c>
       <c r="U13" t="n">
-        <v>1.135616046880445</v>
+        <v>1.158276255028514</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>24</v>
       </c>
       <c r="U14" t="n">
-        <v>1.135616046880445</v>
+        <v>1.158276255028514</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>24</v>
       </c>
       <c r="U15" t="n">
-        <v>1.146083847487058</v>
+        <v>1.170160055349176</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>24</v>
       </c>
       <c r="U16" t="n">
-        <v>1.161244178101981</v>
+        <v>1.186608909233928</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>24</v>
       </c>
       <c r="U17" t="n">
-        <v>1.161244178101981</v>
+        <v>1.186608909233928</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>24</v>
       </c>
       <c r="U18" t="n">
-        <v>1.180815190317274</v>
+        <v>1.2073364299059</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>24</v>
       </c>
       <c r="U19" t="n">
-        <v>1.204715155958085</v>
+        <v>1.232257857465449</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.158599285593576</v>
+        <v>1.185515460468151</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>24</v>
       </c>
       <c r="U21" t="n">
-        <v>1.118275403134967</v>
+        <v>1.144381169815628</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>24</v>
       </c>
       <c r="U22" t="n">
-        <v>1.084389839970526</v>
+        <v>1.109478928030659</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>24</v>
       </c>
       <c r="U23" t="n">
-        <v>1.065342139311574</v>
+        <v>1.090881932567388</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>24</v>
       </c>
       <c r="U24" t="n">
-        <v>1.046433433155172</v>
+        <v>1.072436383814983</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>24</v>
       </c>
       <c r="U25" t="n">
-        <v>1.02770222402413</v>
+        <v>1.054430646841074</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>24</v>
       </c>
       <c r="U26" t="n">
-        <v>1.012807495880597</v>
+        <v>1.04005833970462</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         <v>24</v>
       </c>
       <c r="U27" t="n">
-        <v>1.000732024614465</v>
+        <v>1.028444023712441</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>24</v>
       </c>
       <c r="U28" t="n">
-        <v>0.9701277512553037</v>
+        <v>0.9968045057091312</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>24</v>
       </c>
       <c r="U29" t="n">
-        <v>0.963467800922458</v>
+        <v>0.988410108076652</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>24</v>
       </c>
       <c r="U30" t="n">
-        <v>1.003182020971497</v>
+        <v>1.026838089863189</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>24</v>
       </c>
       <c r="U31" t="n">
-        <v>1.065754178920031</v>
+        <v>1.089606397511805</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>24</v>
       </c>
       <c r="U32" t="n">
-        <v>1.141089185550069</v>
+        <v>1.16485299373448</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>24</v>
       </c>
       <c r="U33" t="n">
-        <v>1.158153690006908</v>
+        <v>1.181563709941387</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>24</v>
       </c>
       <c r="U34" t="n">
-        <v>1.15819988387575</v>
+        <v>1.181609300853168</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>24</v>
       </c>
       <c r="U35" t="n">
-        <v>1.102254072661868</v>
+        <v>1.12699132816062</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>24</v>
       </c>
       <c r="U36" t="n">
-        <v>1.096254831352987</v>
+        <v>1.122941688267773</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>24</v>
       </c>
       <c r="U37" t="n">
-        <v>1.07864432404829</v>
+        <v>1.105767649393635</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>24</v>
       </c>
       <c r="U38" t="n">
-        <v>1.07864432404829</v>
+        <v>1.105767649393635</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>24</v>
       </c>
       <c r="U39" t="n">
-        <v>1.279130714889335</v>
+        <v>1.301978263707958</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>24</v>
       </c>
       <c r="U40" t="n">
-        <v>1.297980914502149</v>
+        <v>1.320492836462016</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>24</v>
       </c>
       <c r="U41" t="n">
-        <v>1.209332583344856</v>
+        <v>1.230346122988791</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>24</v>
       </c>
       <c r="U42" t="n">
-        <v>1.144990862904984</v>
+        <v>1.16560825327576</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>24</v>
       </c>
       <c r="U43" t="n">
-        <v>1.085947656534215</v>
+        <v>1.107698626286902</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>24</v>
       </c>
       <c r="U44" t="n">
-        <v>0.8042465283233221</v>
+        <v>0.8336086984618074</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>24</v>
       </c>
       <c r="U45" t="n">
-        <v>0.7183597115806868</v>
+        <v>0.7511706479545588</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>24</v>
       </c>
       <c r="U46" t="n">
-        <v>0.7883867045099943</v>
+        <v>0.8184954356762562</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -3848,11 +3848,11 @@
         <v>24</v>
       </c>
       <c r="U47" t="n">
-        <v>0.8395319544370146</v>
+        <v>0.8735610037215538</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3920,11 +3920,11 @@
         <v>24</v>
       </c>
       <c r="U48" t="n">
-        <v>0.8227795055154115</v>
+        <v>0.8552776645182807</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -3992,11 +3992,11 @@
         <v>24</v>
       </c>
       <c r="U49" t="n">
-        <v>0.8284733934519233</v>
+        <v>0.8585543895128992</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -4064,11 +4064,11 @@
         <v>24</v>
       </c>
       <c r="U50" t="n">
-        <v>0.8284733934519232</v>
+        <v>0.858554389512899</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
         <v>24</v>
       </c>
       <c r="U51" t="n">
-        <v>0.7547263100434298</v>
+        <v>0.7877086786756923</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>24</v>
       </c>
       <c r="U52" t="n">
-        <v>0.6682984582067444</v>
+        <v>0.6984966581924287</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>24</v>
       </c>
       <c r="U53" t="n">
-        <v>0.6462251616110682</v>
+        <v>0.6802155107436838</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>24</v>
       </c>
       <c r="U59" t="n">
-        <v>0.5481210026853661</v>
+        <v>0.5881485917778658</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>24</v>
       </c>
       <c r="U60" t="n">
-        <v>0.5274765317668819</v>
+        <v>0.5720677120379717</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>24</v>
       </c>
       <c r="U61" t="n">
-        <v>0.5286317679385046</v>
+        <v>0.573156291147972</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>24</v>
       </c>
       <c r="U62" t="n">
-        <v>0.5304036863351661</v>
+        <v>0.5748128348825079</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>24</v>
       </c>
       <c r="U63" t="n">
-        <v>0.5304036863351661</v>
+        <v>0.574812834882508</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>24</v>
       </c>
       <c r="U64" t="n">
-        <v>0.4875947711777382</v>
+        <v>0.5359828726007227</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>24</v>
       </c>
       <c r="U65" t="n">
-        <v>0.5136885529485012</v>
+        <v>0.5565228535434843</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>24</v>
       </c>
       <c r="U66" t="n">
-        <v>0.5664019880410591</v>
+        <v>0.6022623341442874</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>24</v>
       </c>
       <c r="U67" t="n">
-        <v>0.6304814373326418</v>
+        <v>0.6627791270880268</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>24</v>
       </c>
       <c r="U68" t="n">
-        <v>0.7073370824819818</v>
+        <v>0.7363564082913699</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>24</v>
       </c>
       <c r="U69" t="n">
-        <v>0.7402660672124738</v>
+        <v>0.7680749542602677</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>24</v>
       </c>
       <c r="U70" t="n">
-        <v>0.7508844095877196</v>
+        <v>0.7807586765128828</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>24</v>
       </c>
       <c r="U71" t="n">
-        <v>0.7869240862054105</v>
+        <v>0.8178317069071344</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -5648,11 +5648,11 @@
         <v>24</v>
       </c>
       <c r="U72" t="n">
-        <v>0.8223510490073919</v>
+        <v>0.8520039345531329</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -5720,11 +5720,11 @@
         <v>24</v>
       </c>
       <c r="U73" t="n">
-        <v>0.8223510490073919</v>
+        <v>0.8520039345531329</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Observation Required (Pattern Change)</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
         <v>24</v>
       </c>
       <c r="U74" t="n">
-        <v>0.8768047471298793</v>
+        <v>0.9047162158693852</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>24</v>
       </c>
       <c r="U75" t="n">
-        <v>0.9677685820195691</v>
+        <v>0.9883559099881438</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>24</v>
       </c>
       <c r="U76" t="n">
-        <v>1.070008991712892</v>
+        <v>1.08884303292683</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>24</v>
       </c>
       <c r="U77" t="n">
-        <v>1.17549367088776</v>
+        <v>1.1928269042421</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>24</v>
       </c>
       <c r="U78" t="n">
-        <v>1.338423468527458</v>
+        <v>1.355064208648813</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>24</v>
       </c>
       <c r="U79" t="n">
-        <v>1.442362533578467</v>
+        <v>1.452473677713847</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>24</v>
       </c>
       <c r="U80" t="n">
-        <v>1.580718829224923</v>
+        <v>1.593023034992715</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>24</v>
       </c>
       <c r="U81" t="n">
-        <v>1.704486912171046</v>
+        <v>1.715948437542611</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>24</v>
       </c>
       <c r="U82" t="n">
-        <v>1.805361224281097</v>
+        <v>1.81622025821159</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>24</v>
       </c>
       <c r="U83" t="n">
-        <v>2.076930160486044</v>
+        <v>2.085666852577167</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>24</v>
       </c>
       <c r="U84" t="n">
-        <v>2.420104300996074</v>
+        <v>2.430958596083433</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>24</v>
       </c>
       <c r="U85" t="n">
-        <v>2.568275768028581</v>
+        <v>2.578540526233434</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>24</v>
       </c>
       <c r="U86" t="n">
-        <v>2.679595388768711</v>
+        <v>2.687346103070916</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>24</v>
       </c>
       <c r="U87" t="n">
-        <v>2.048098686686878</v>
+        <v>2.058045616797096</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>24</v>
       </c>
       <c r="U88" t="n">
-        <v>1.226171436221932</v>
+        <v>1.242205224769514</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>24</v>
       </c>
       <c r="U89" t="n">
-        <v>0.651234200528066</v>
+        <v>0.6797778719280767</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>24</v>
       </c>
       <c r="U90" t="n">
-        <v>0.4242097158661651</v>
+        <v>0.7939864003111219</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>24</v>
       </c>
       <c r="U91" t="n">
-        <v>1.478806456886202</v>
+        <v>1.463413700635962</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>24</v>
       </c>
       <c r="U92" t="n">
-        <v>1.443456947314797</v>
+        <v>1.427702015038671</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>24</v>
       </c>
       <c r="U93" t="n">
-        <v>1.408529416986689</v>
+        <v>1.392398179568708</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>24</v>
       </c>
       <c r="U94" t="n">
-        <v>1.344358327288864</v>
+        <v>1.326170543407412</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>24</v>
       </c>
       <c r="U95" t="n">
-        <v>1.244598485682982</v>
+        <v>1.226637630166874</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>24</v>
       </c>
       <c r="U96" t="n">
-        <v>1.110786385734004</v>
+        <v>1.114955980294949</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>24</v>
       </c>
       <c r="U97" t="n">
-        <v>1.131319411003321</v>
+        <v>1.136925981124531</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>24</v>
       </c>
       <c r="U98" t="n">
-        <v>1.111324431662898</v>
+        <v>1.11704261597889</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>24</v>
       </c>
       <c r="U99" t="n">
-        <v>1.129032233011956</v>
+        <v>1.127827320057895</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>24</v>
       </c>
       <c r="U100" t="n">
-        <v>1.13434944817579</v>
+        <v>1.150009908010259</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>24</v>
       </c>
       <c r="U101" t="n">
-        <v>1.076222130568177</v>
+        <v>1.087688510201708</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>24</v>
       </c>
       <c r="U102" t="n">
-        <v>1.008470108535636</v>
+        <v>1.019049302707817</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>24</v>
       </c>
       <c r="U103" t="n">
-        <v>0.9673355109334674</v>
+        <v>0.9783852950501492</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
